--- a/data/trans_dic/IP12B$cabeza-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,32</t>
+          <t>0,0; 37,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,38</t>
+          <t>0,0; 22,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,07</t>
+          <t>0,0; 39,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,77</t>
+          <t>0,0; 54,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,99</t>
+          <t>0,0; 20,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,21</t>
+          <t>0,0; 20,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,68</t>
+          <t>0,0; 38,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,54</t>
+          <t>0,0; 63,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,05</t>
+          <t>0,0; 45,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,11</t>
+          <t>0,0; 25,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,69</t>
+          <t>0,0; 22,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,19</t>
+          <t>0,0; 29,01</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,22</t>
+          <t>0,0; 19,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,09</t>
+          <t>0,0; 28,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,81</t>
+          <t>0,0; 23,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,96</t>
+          <t>0,0; 26,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 15,45</t>
+          <t>1,67; 16,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 20,07</t>
+          <t>2,07; 19,71</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,82</t>
+          <t>0,0; 50,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,72</t>
+          <t>0,0; 34,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,0</t>
+          <t>0,0; 58,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,21</t>
+          <t>0,0; 30,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,64</t>
+          <t>0,0; 18,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,81</t>
+          <t>0,0; 24,52</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 80,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,43</t>
+          <t>0,0; 35,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 14,13</t>
+          <t>1,52; 14,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,43</t>
+          <t>2,21; 11,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 15,05</t>
+          <t>1,36; 14,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,89</t>
+          <t>0,0; 9,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,26</t>
+          <t>1,17; 10,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,61</t>
+          <t>0,0; 12,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,12</t>
+          <t>1,51; 9,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 9,15</t>
+          <t>2,12; 9,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 9,91</t>
+          <t>1,27; 9,36</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3244</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3229</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2612</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3035</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2640</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3567</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2932</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2856</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3146</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2816</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3530</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2774</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2822</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3430</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5907</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5372</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4537</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>666; 6426</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>776; 7376</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4122</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4124</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4375</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4405</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4025</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4341</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2348</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3317</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2158</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3517</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2531</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3475</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4340</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>629; 5910</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1343; 7207</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>719; 7402</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4515</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>685; 6261</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5960</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1329; 8406</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2526; 11558</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1250; 9243</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$cabeza-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,49</t>
+          <t>0,0; 37,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,41</t>
+          <t>0,0; 20,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,95</t>
+          <t>0,0; 39,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,35</t>
+          <t>0,0; 51,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,96</t>
+          <t>0,0; 28,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,13</t>
+          <t>0,0; 19,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,84</t>
+          <t>0,0; 40,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,02</t>
+          <t>0,0; 57,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,81</t>
+          <t>0,0; 40,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,08</t>
+          <t>0,0; 24,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,94</t>
+          <t>0,0; 23,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,01</t>
+          <t>0,0; 28,46</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,75</t>
+          <t>0,0; 19,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,74</t>
+          <t>0,0; 27,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,77</t>
+          <t>0,0; 23,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,89</t>
+          <t>0,0; 26,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 16,08</t>
+          <t>1,65; 16,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 19,71</t>
+          <t>2,11; 19,87</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,11</t>
+          <t>0,0; 48,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,1</t>
+          <t>0,0; 34,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,86</t>
+          <t>0,0; 48,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,94</t>
+          <t>0,0; 31,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,55</t>
+          <t>0,0; 18,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,52</t>
+          <t>0,0; 24,49</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,84</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,65</t>
+          <t>0,0; 35,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 14,25</t>
+          <t>1,53; 13,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 11,88</t>
+          <t>2,22; 13,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 14,02</t>
+          <t>1,18; 13,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,67</t>
+          <t>0,0; 10,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,68</t>
+          <t>1,17; 10,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,97</t>
+          <t>0,0; 11,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,53</t>
+          <t>1,49; 9,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 9,69</t>
+          <t>2,37; 9,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 9,36</t>
+          <t>1,59; 9,96</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3244</t>
+          <t>0; 3279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3229</t>
+          <t>0; 2974</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2612</t>
+          <t>0; 2599</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3035</t>
+          <t>0; 2857</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2640</t>
+          <t>0; 3608</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3567</t>
+          <t>0; 3492</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2932</t>
+          <t>0; 3032</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2856</t>
+          <t>0; 2627</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3146</t>
+          <t>0; 2756</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2816</t>
+          <t>0; 2776</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3530</t>
+          <t>0; 3604</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2774</t>
+          <t>0; 2722</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3430</t>
+          <t>0; 3333</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5907</t>
+          <t>0; 5588</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5372</t>
+          <t>0; 5313</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4537</t>
+          <t>0; 4427</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>666; 6426</t>
+          <t>658; 6560</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>776; 7376</t>
+          <t>789; 7437</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4122</t>
+          <t>0; 4002</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4124</t>
+          <t>0; 4142</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2316,22 +2316,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4375</t>
+          <t>0; 3600</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4405</t>
+          <t>0; 4545</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4025</t>
+          <t>0; 4042</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4341</t>
+          <t>0; 4336</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2348</t>
+          <t>0; 2905</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3317</t>
+          <t>0; 3264</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>629; 5910</t>
+          <t>635; 5580</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1343; 7207</t>
+          <t>1349; 8198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>719; 7402</t>
+          <t>620; 6934</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4515</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>685; 6261</t>
+          <t>688; 6184</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5960</t>
+          <t>0; 5467</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1329; 8406</t>
+          <t>1313; 8481</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2526; 11558</t>
+          <t>2830; 11165</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1250; 9243</t>
+          <t>1571; 9831</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$cabeza-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 37,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,64</t>
+          <t>0,0; 22,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,67%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 54,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 49,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,64</t>
+          <t>0,0; 27,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,7</t>
+          <t>0,0; 20,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,43%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,82%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 51,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,72</t>
+          <t>0,0; 30,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,42</t>
+          <t>0,0; 18,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,46</t>
+          <t>0,0; 35,19</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,85%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,27%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,2</t>
+          <t>0,0; 25,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,19</t>
+          <t>0,0; 22,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,51</t>
+          <t>0,0; 21,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,23</t>
+          <t>0,0; 27,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 16,42</t>
+          <t>1,68; 15,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 19,87</t>
+          <t>2,08; 20,07</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>18,55%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>10,89%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 47,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 47,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 32,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,92</t>
+          <t>0,0; 33,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,63</t>
+          <t>0,0; 18,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,49</t>
+          <t>0,0; 24,81</t>
         </is>
       </c>
     </row>
@@ -1180,22 +1180,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>28,17%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,24 +1233,24 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,09</t>
+          <t>0,0; 39,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5,2%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5,8%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4,79%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 13,45</t>
+          <t>0,0; 8,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 13,51</t>
+          <t>1,18; 11,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 13,13</t>
+          <t>0,0; 13,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,05</t>
+          <t>1,51; 14,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,55</t>
+          <t>2,2; 12,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,9</t>
+          <t>1,2; 15,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 9,62</t>
+          <t>1,49; 8,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 9,36</t>
+          <t>2,41; 9,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,96</t>
+          <t>1,72; 9,91</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>638</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3230</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3279</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2974</t>
+          <t>0; 3224</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1696,14 +1696,14 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1749,27 +1749,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2599</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3059</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3209</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2857</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3608</t>
+          <t>0; 3526</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3492</t>
+          <t>0; 3582</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>680</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>626</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2751</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2627</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2756</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3071</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2336</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2776</t>
+          <t>0; 3382</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3604</t>
+          <t>0; 2875</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2722</t>
+          <t>0; 3365</t>
         </is>
       </c>
     </row>
@@ -2027,27 +2027,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2080,27 +2080,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1905</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1781</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>917</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3333</t>
+          <t>0; 5834</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5588</t>
+          <t>0; 3874</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5313</t>
+          <t>0; 3685</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4427</t>
+          <t>0; 5567</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>658; 6560</t>
+          <t>672; 6175</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>789; 7437</t>
+          <t>779; 7513</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1526</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1317</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4142</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3493</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3934</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3957</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3600</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4545</t>
+          <t>0; 4729</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4042</t>
+          <t>0; 4044</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4336</t>
+          <t>0; 4393</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2353,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2406,22 +2406,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>818</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2459,24 +2459,24 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0; 2905</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3264</t>
+          <t>0; 3668</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2158</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>3517</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2531</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2472</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1809</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>635; 5580</t>
+          <t>0; 4153</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1349; 8198</t>
+          <t>693; 6600</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>620; 6934</t>
+          <t>0; 6255</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>626; 5860</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>688; 6184</t>
+          <t>1333; 7540</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5467</t>
+          <t>633; 7946</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1313; 8481</t>
+          <t>1311; 7159</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2830; 11165</t>
+          <t>2871; 10920</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1571; 9831</t>
+          <t>1700; 9785</t>
         </is>
       </c>
     </row>
